--- a/artfynd/A 14044-2024 artfynd.xlsx
+++ b/artfynd/A 14044-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97387070</v>
+        <v>97387037</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564281.7531911775</v>
+        <v>564259</v>
       </c>
       <c r="R2" t="n">
-        <v>6355885.050342115</v>
+        <v>6356029</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,24 +743,14 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Mindre förekomst på block</t>
+          <t>Riklig på smal murken gren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97387086</v>
+        <v>97387068</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564269.4860458274</v>
+        <v>564231</v>
       </c>
       <c r="R3" t="n">
-        <v>6355908.606168455</v>
+        <v>6356039</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,19 +845,14 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Större förekomst på block</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97387068</v>
+        <v>97387069</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564230.6817363802</v>
+        <v>564255</v>
       </c>
       <c r="R4" t="n">
-        <v>6356038.071106714</v>
+        <v>6355986</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -977,24 +947,14 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Större förekomst på block</t>
+          <t>Mindre förekomst på block</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97387085</v>
+        <v>97387070</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564262.4042689597</v>
+        <v>564281</v>
       </c>
       <c r="R5" t="n">
-        <v>6355980.81868752</v>
+        <v>6355885</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1094,19 +1049,14 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mindre förekomst på block</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97387069</v>
+        <v>97387475</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,34 +1094,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Vädern, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564254.2183296299</v>
+        <v>564255</v>
       </c>
       <c r="R6" t="n">
-        <v>6355985.5477651</v>
+        <v>6355889</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1208,7 +1157,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1167,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mindre förekomst på block</t>
+          <t>stöttes i skogskant</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97387469</v>
+        <v>97387468</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1229,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1299,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564240.6797540444</v>
+        <v>564265</v>
       </c>
       <c r="R7" t="n">
-        <v>6355883.326433189</v>
+        <v>6356010</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1371,43 +1315,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97387094</v>
+        <v>97387469</v>
       </c>
       <c r="B8" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564272.1177395452</v>
+        <v>564241</v>
       </c>
       <c r="R8" t="n">
-        <v>6356016.592735763</v>
+        <v>6355884</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1451,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnag på liggande död glasbjörk</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,47 +1431,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97387468</v>
+        <v>97387093</v>
       </c>
       <c r="B9" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1542,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564265.1909538282</v>
+        <v>564230</v>
       </c>
       <c r="R9" t="n">
-        <v>6356010.007401957</v>
+        <v>6356083</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1575,19 +1504,14 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:32</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gnag på stående död glasbjörk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,50 +1538,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97387037</v>
+        <v>97387094</v>
       </c>
       <c r="B10" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Vädern, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564260.0288187279</v>
+        <v>564272</v>
       </c>
       <c r="R10" t="n">
-        <v>6356028.816563182</v>
+        <v>6356017</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1687,24 +1611,14 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig på smal murken gren</t>
+          <t>Gnag på liggande död glasbjörk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,54 +1645,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97387475</v>
+        <v>97387085</v>
       </c>
       <c r="B11" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Vädern, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564254.6438682346</v>
+        <v>564263</v>
       </c>
       <c r="R11" t="n">
-        <v>6355889.48258038</v>
+        <v>6355981</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1808,24 +1713,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>07:23</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>07:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>stöttes i skogskant</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,6 +1739,103 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97387086</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stora Vädern, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564269</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6355909</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14044-2024 artfynd.xlsx
+++ b/artfynd/A 14044-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387037</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387068</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387070</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387475</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387468</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387469</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387093</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387094</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387085</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1836,8 +1891,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>